--- a/Assets/Resources/Configs/HeroConfig.xlsx
+++ b/Assets/Resources/Configs/HeroConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProgram\SoulFighterSurvivor\Assets\Resources\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4D71BF-94D5-42C2-BDC8-63FAF25FEC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805B7F99-457F-4578-923A-387F822BABAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="25845" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -111,10 +111,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Ryze</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>heroName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -155,26 +151,6 @@
   </si>
   <si>
     <t>SpiritRush</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArcaneMastery</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overload</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RunePrison</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpellFlux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RealmWarp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -559,14 +535,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="20.58203125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultColWidth="20.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.08203125" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="20.58203125" style="1"/>
+    <col min="1" max="1" width="26.125" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="20.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -579,28 +555,22 @@
       <c r="D1" s="1">
         <v>3</v>
       </c>
-      <c r="E1" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -608,16 +578,13 @@
         <v>590</v>
       </c>
       <c r="C3" s="1">
-        <v>645</v>
+        <v>590</v>
       </c>
       <c r="D3" s="1">
-        <v>590</v>
-      </c>
-      <c r="E3" s="1">
         <v>630</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -625,16 +592,13 @@
         <v>418</v>
       </c>
       <c r="C4" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1">
         <v>349</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -642,16 +606,13 @@
         <v>53</v>
       </c>
       <c r="C5" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D5" s="1">
-        <v>60</v>
-      </c>
-      <c r="E5" s="1">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -659,16 +620,13 @@
         <v>0.66800000000000004</v>
       </c>
       <c r="C6" s="1">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="D6" s="1">
         <v>0.65800000000000003</v>
       </c>
-      <c r="D6" s="1">
-        <v>0.69699999999999995</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.65800000000000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -676,16 +634,13 @@
         <v>21</v>
       </c>
       <c r="C7" s="1">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1">
-        <v>32</v>
-      </c>
-      <c r="E7" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -696,13 +651,10 @@
         <v>32</v>
       </c>
       <c r="D8" s="1">
-        <v>32</v>
-      </c>
-      <c r="E8" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -710,16 +662,13 @@
         <v>2.5</v>
       </c>
       <c r="C9" s="1">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="D9" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="E9" s="1">
         <v>3.25</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -727,16 +676,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -744,16 +690,13 @@
         <v>550</v>
       </c>
       <c r="C11" s="1">
-        <v>550</v>
+        <v>175</v>
       </c>
       <c r="D11" s="1">
-        <v>175</v>
-      </c>
-      <c r="E11" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -761,16 +704,13 @@
         <v>330</v>
       </c>
       <c r="C12" s="1">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D12" s="1">
-        <v>345</v>
-      </c>
-      <c r="E12" s="1">
         <v>335</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -783,11 +723,8 @@
       <c r="D13" s="1">
         <v>100</v>
       </c>
-      <c r="E13" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -795,16 +732,13 @@
         <v>104</v>
       </c>
       <c r="C14" s="1">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D14" s="1">
-        <v>110</v>
-      </c>
-      <c r="E14" s="1">
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -812,16 +746,13 @@
         <v>25</v>
       </c>
       <c r="C15" s="1">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -834,11 +765,8 @@
       <c r="D16" s="1">
         <v>3</v>
       </c>
-      <c r="E16" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -846,16 +774,13 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="C17" s="1">
-        <v>2.1100000000000001E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="D17" s="1">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="E17" s="1">
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -863,16 +788,13 @@
         <v>4.7</v>
       </c>
       <c r="C18" s="1">
-        <v>4.2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D18" s="1">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="E18" s="1">
         <v>4.7</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -880,16 +802,13 @@
         <v>1.3</v>
       </c>
       <c r="C19" s="1">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="D19" s="1">
         <v>1.3</v>
       </c>
-      <c r="D19" s="1">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -897,16 +816,13 @@
         <v>0.6</v>
       </c>
       <c r="C20" s="1">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D20" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="E20" s="1">
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -914,132 +830,108 @@
         <v>0.8</v>
       </c>
       <c r="C21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1">
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B22" s="1">
         <v>0.2</v>
       </c>
       <c r="C22" s="1">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="D22" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="E22" s="1">
         <v>0.15</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1">
         <v>0.625</v>
       </c>
       <c r="C23" s="1">
-        <v>0.625</v>
+        <v>0.67</v>
       </c>
       <c r="D23" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="E23" s="1">
         <v>0.65800000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
